--- a/DataTables/DetailText/剧情/025_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/025_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7855D3D-E41E-497C-88F0-4CD8A7433C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3796D9-4752-46F9-924F-223A6FB4CADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,17 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -371,7 +360,37 @@
   </si>
   <si>
     <r>
-      <t>022治</t>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_02</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>025_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>025治</t>
     </r>
     <r>
       <rPr>
@@ -393,36 +412,6 @@
       </rPr>
       <t>成功</t>
     </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>_02</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>025_01</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -430,11 +419,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -448,7 +437,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -469,7 +458,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -632,7 +621,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -911,27 +900,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -981,12 +970,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1000,7 +989,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1015,65 +1004,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="14"/>
       <c r="L3" s="17"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8" ht="18.75">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -1085,20 +1074,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1124,7 +1113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1146,7 +1135,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1168,7 +1157,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1188,7 +1177,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1210,7 +1199,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1230,7 +1219,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1254,7 +1243,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1274,7 +1263,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1294,7 +1283,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1314,7 +1303,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1334,7 +1323,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1354,7 +1343,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8">
       <c r="A13" s="1"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>

--- a/DataTables/DetailText/剧情/025_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/025_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3796D9-4752-46F9-924F-223A6FB4CADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB6B586-D605-461A-B7F0-4EDFB7B47920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -419,11 +430,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -437,7 +448,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -458,7 +469,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -621,7 +632,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -900,27 +911,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -970,7 +981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>47</v>
       </c>
@@ -1004,65 +1015,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10"/>
       <c r="H3" s="14"/>
       <c r="L3" s="17"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" ht="18.75">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -1074,20 +1085,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1113,7 +1124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1123,8 +1134,8 @@
       <c r="C2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
+      <c r="D2" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
@@ -1135,7 +1146,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1157,7 +1168,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1167,8 +1178,8 @@
       <c r="C4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
+      <c r="D4" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
@@ -1177,7 +1188,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1199,7 +1210,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1209,8 +1220,8 @@
       <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
+      <c r="D6" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -1219,7 +1230,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1243,7 +1254,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1253,8 +1264,8 @@
       <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>39</v>
+      <c r="D8" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1263,7 +1274,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1273,8 +1284,8 @@
       <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
+      <c r="D9" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1283,7 +1294,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1303,7 +1314,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1313,8 +1324,8 @@
       <c r="C11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>39</v>
+      <c r="D11" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1323,7 +1334,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1343,7 +1354,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>

--- a/DataTables/DetailText/剧情/025_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/025_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB6B586-D605-461A-B7F0-4EDFB7B47920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B021F11E-CDB1-4CD2-86E7-AA8D7E21CDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>StoryID</t>
   </si>
@@ -225,8 +225,74 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>是是是，</t>
+    <t>半夏</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哇，这就是传说中的花和尚吗？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陈皮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>找打！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哎哟！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>after</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_02</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>025_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>025治</t>
     </r>
     <r>
       <rPr>
@@ -236,7 +302,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>师</t>
+      <t>疗</t>
     </r>
     <r>
       <rPr>
@@ -246,7 +312,13 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>傅</t>
+      <t>成功</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>是是是，</t>
     </r>
     <r>
       <rPr>
@@ -256,7 +328,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>说</t>
+      <t>师父说</t>
     </r>
     <r>
       <rPr>
@@ -319,7 +391,7 @@
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>嗯，以后可别乱说啊，这小郎中真是</t>
+      <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是</t>
     </r>
     <r>
       <rPr>
@@ -334,95 +406,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>半夏</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>mid</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哇，这就是传说中的花和尚吗？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>hide</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>陈皮</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>他是花和尚，你是花痴，正好凑一对儿。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>找打！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哎哟！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>after</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>_02</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>025_01</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>025治</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>疗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>成功</t>
-    </r>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>金钱+2两</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -577,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -628,6 +615,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -983,10 +973,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1000,7 +990,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1084,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -1135,7 +1125,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
@@ -1160,7 +1150,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
@@ -1179,7 +1169,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
@@ -1202,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1221,13 +1211,13 @@
         <v>31</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1244,14 +1234,14 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="19" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1259,19 +1249,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>40</v>
+      <c r="H8" s="20" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1281,17 +1267,17 @@
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
+      <c r="C9" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1301,17 +1287,17 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1322,16 +1308,16 @@
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>9</v>
+        <v>40</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1342,27 +1328,47 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/025_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/025_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B021F11E-CDB1-4CD2-86E7-AA8D7E21CDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732743AD-4F4C-4D99-8DC5-A5782C97DC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
   <si>
     <t>LineIndex</t>
   </si>
@@ -80,66 +66,16 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
     <t>clinic</t>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>current_scene</t>
-  </si>
-  <si>
-    <t>story_npc_cured</t>
   </si>
   <si>
     <t>性空</t>
@@ -412,16 +348,104 @@
     <t>金钱+2两</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>cured</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -435,7 +459,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -456,20 +480,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -504,8 +520,30 @@
       <family val="3"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -520,20 +558,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -564,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -590,39 +630,56 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -900,174 +957,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="23" customFormat="1">
+      <c r="A1" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q1" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="23" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="M2" s="24"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="10"/>
-      <c r="H3" s="14"/>
-      <c r="L3" s="17"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="10"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="10"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="10"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="10"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="14"/>
+      <c r="T2" s="25"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="L3" s="12"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="9"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="9"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="9"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="9"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{3E5A84D7-2969-4168-AEF6-CA5B7AD9CECE}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{9661F810-60D0-4447-AA74-B03D5269E99C}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{E7611C22-4D0A-41E0-A71E-3736925298D2}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{069A50DA-9765-4228-927F-7F1D2C368889}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{D86E467E-BFD2-4A5B-B287-6B9D8B236E97}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1075,292 +1159,292 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H7" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>

--- a/DataTables/DetailText/剧情/025_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/025_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732743AD-4F4C-4D99-8DC5-A5782C97DC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9C4FAC-C6D3-4A7C-9142-A8CA56563040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18975" yWindow="4845" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="57">
   <si>
     <t>LineIndex</t>
   </si>
@@ -436,6 +447,10 @@
   <si>
     <t>cured</t>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="12"/>
+  </si>
 </sst>
 </file>
 
@@ -445,7 +460,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -459,7 +474,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -480,7 +495,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -604,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -677,9 +692,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -958,25 +976,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="23" customFormat="1">
+    <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>37</v>
       </c>
@@ -1038,7 +1056,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1">
+    <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>30</v>
       </c>
@@ -1158,21 +1176,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="67.125" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1197,8 +1215,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1219,8 +1240,9 @@
       <c r="H2" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1241,8 +1263,9 @@
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1261,8 +1284,9 @@
       <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1283,8 +1307,9 @@
       <c r="H5" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1303,8 +1328,9 @@
       <c r="H6" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1327,8 +1353,9 @@
       <c r="H7" s="14" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1343,8 +1370,9 @@
       <c r="H8" s="15" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1363,8 +1391,9 @@
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1383,8 +1412,9 @@
       <c r="H10" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1403,8 +1433,9 @@
       <c r="H11" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1423,8 +1454,9 @@
       <c r="H12" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1443,8 +1475,9 @@
       <c r="H13" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1453,6 +1486,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
+      <c r="I14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/025_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/025_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9C4FAC-C6D3-4A7C-9142-A8CA56563040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA68F3C-4DFB-4E18-9A77-110463CB65F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18975" yWindow="4845" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -97,6 +97,87 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一定是我晚上念经太过用功，着凉了。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半夏</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哇，这就是传说中的花和尚吗？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陈皮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>找打！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哎哟！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>after</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_02</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>025_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>025治</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -105,7 +186,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>师</t>
+      <t>疗</t>
     </r>
     <r>
       <rPr>
@@ -115,7 +196,152 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>傅所患的乃是</t>
+      <t>成功</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>金钱+2两</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>cured</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>师父</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>所患的乃是</t>
     </r>
     <r>
       <rPr>
@@ -128,7 +354,7 @@
       <t>肾精不足之症，嗯…是房事过劳所致…</t>
     </r>
     <rPh sb="1" eb="2">
-      <t>ツ</t>
+      <t>チチ</t>
     </rPh>
     <rPh sb="2" eb="3">
       <t>ショ</t>
@@ -160,86 +386,8 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>…</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>一定是我晚上念经太过用功，着凉了。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>半夏</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>mid</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哇，这就是传说中的花和尚吗？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>hide</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>陈皮</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>他是花和尚，你是花痴，正好凑一对儿。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>找打！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哎哟！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>after</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>_02</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>025_01</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>025治</t>
+    <r>
+      <t>是是是，</t>
     </r>
     <r>
       <rPr>
@@ -249,53 +397,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>疗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>成功</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>是是是，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>师父说</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对</t>
+      <t>师父说得对</t>
     </r>
     <r>
       <rPr>
@@ -328,128 +430,6 @@
       <t>个可能。</t>
     </r>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>…</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>subtitle</t>
-  </si>
-  <si>
-    <t>金钱+2两</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>剧情ID</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>剧情名</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>触发场景</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>触发天数</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <r>
-      <t>金</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>钱判定</t>
-    </r>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>触发金钱</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>名望判定</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>触发名望</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>触发条目</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>触发剧情ID</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>触发治疗结果</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>播放后</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>人物ID</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>疾病</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>人物立绘路径</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>奖励金钱</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>奖励名望</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>奖励心得</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>cured</t>
-  </si>
-  <si>
-    <t>Music</t>
-    <phoneticPr fontId="12"/>
   </si>
 </sst>
 </file>
@@ -996,58 +976,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="F1" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="K1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="M1" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="N1" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="P1" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="Q1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="R1" s="21" t="s">
         <v>52</v>
-      </c>
-      <c r="Q1" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="R1" s="21" t="s">
-        <v>54</v>
       </c>
       <c r="S1" s="22" t="s">
         <v>11</v>
@@ -1058,10 +1038,10 @@
     </row>
     <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -1071,10 +1051,10 @@
       <c r="H2" s="13"/>
       <c r="I2" s="24"/>
       <c r="J2" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>13</v>
@@ -1082,7 +1062,9 @@
       <c r="M2" s="24"/>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
+      <c r="P2" s="13">
+        <v>2000</v>
+      </c>
       <c r="Q2" s="13"/>
       <c r="R2" s="25"/>
       <c r="S2" s="25" t="b">
@@ -1216,7 +1198,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1230,7 +1212,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
@@ -1238,7 +1220,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1256,12 +1238,12 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1276,13 +1258,13 @@
         <v>16</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1300,12 +1282,12 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1320,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1344,14 +1326,14 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -1360,7 +1342,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2"/>
@@ -1368,7 +1350,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1380,7 +1362,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
@@ -1389,7 +1371,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -1404,13 +1386,13 @@
         <v>16</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1422,7 +1404,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>7</v>
@@ -1431,7 +1413,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1443,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>8</v>
@@ -1452,7 +1434,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -1464,7 +1446,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>7</v>
@@ -1473,7 +1455,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I13" s="1"/>
     </row>
